--- a/tests/coil_3D_avoltemf_ferr/input_template.xlsx
+++ b/tests/coil_3D_avoltemf_ferr/input_template.xlsx
@@ -219,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -237,6 +237,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
@@ -560,7 +566,7 @@
       <c r="A1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="9" t="s">
         <v>44</v>
       </c>
       <c r="C1" s="3" t="s">
@@ -649,13 +655,27 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="A5" s="3">
+        <v>26</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -708,7 +728,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="20.14785714285714" customWidth="1" bestFit="1"/>
@@ -819,35 +839,67 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="3">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="7">
+        <v>26</v>
+      </c>
+      <c r="B4" s="8">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1</v>
+      </c>
+      <c r="D4" s="8">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8">
+        <v>1</v>
+      </c>
+      <c r="G4" s="8">
+        <v>1</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="3">
         <v>24</v>
       </c>
-      <c r="B4" s="2">
-        <v>1</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2">
-        <v>2e-8</v>
-      </c>
-      <c r="F4" s="2">
-        <v>2e-8</v>
-      </c>
-      <c r="G4" s="2">
-        <v>2e-8</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2">
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1.09e-7</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1.09e-7</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1.09e-7</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>

--- a/tests/coil_3D_avoltemf_ferr/input_template.xlsx
+++ b/tests/coil_3D_avoltemf_ferr/input_template.xlsx
@@ -177,7 +177,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,6 +188,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -239,10 +245,10 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
@@ -602,7 +608,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="3">
         <v>0</v>
@@ -625,7 +631,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -648,7 +654,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -671,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
